--- a/OUTPUT/direct_A1B3Z0_Paracoccus_denitrificans_PD1222.xlsx
+++ b/OUTPUT/direct_A1B3Z0_Paracoccus_denitrificans_PD1222.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0218</v>
+        <v>0.02199120351859256</v>
       </c>
     </row>
   </sheetData>
